--- a/outputs/49801.xlsx
+++ b/outputs/49801.xlsx
@@ -98,17 +98,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -311,11 +315,11 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="str">
+      <c r="B1" s="3" t="str">
         <f aca="false">LEFT(A1,2)</f>
         <v>SL</v>
       </c>
-      <c r="C1" s="0" t="str">
+      <c r="C1" s="3" t="str">
         <f aca="false">LEFT(A1,2)&amp;RIGHT(A1,5)</f>
         <v>SL-0035</v>
       </c>

--- a/outputs/49801.xlsx
+++ b/outputs/49801.xlsx
@@ -320,7 +320,7 @@
         <v>SL</v>
       </c>
       <c r="C1" s="3" t="str">
-        <f aca="false">LEFT(A1,2)&amp;RIGHT(A1,5)</f>
+        <f aca="false">CONCATENATE(LEFT(A1,2),RIGHT(A1,5))</f>
         <v>SL-0035</v>
       </c>
     </row>
